--- a/public/template.xlsx
+++ b/public/template.xlsx
@@ -1,78 +1,185 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC4E347-F1C2-4F54-AE77-D555959DC2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주문데이터" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="로고이미지" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
+  <si>
+    <t>주문확인</t>
+  </si>
+  <si>
+    <t>티셔츠 작업용</t>
+  </si>
+  <si>
+    <t>카드 포장용</t>
+  </si>
+  <si>
+    <t>택배송장정보</t>
+  </si>
+  <si>
+    <t>작업지시번호</t>
+  </si>
+  <si>
+    <t>주문번호</t>
+  </si>
+  <si>
+    <t>납기 발송일</t>
+  </si>
+  <si>
+    <t>티셔츠 사이즈</t>
+  </si>
+  <si>
+    <t>티셔츠 컬러</t>
+  </si>
+  <si>
+    <t>티셔츠 종류</t>
+  </si>
+  <si>
+    <t>티셔츠 일련번호</t>
+  </si>
+  <si>
+    <t>실리콘 마크QR값</t>
+  </si>
+  <si>
+    <t>디자인QR값</t>
+  </si>
+  <si>
+    <t>홀로그램QR값</t>
+  </si>
+  <si>
+    <t>카드 바코드값</t>
+  </si>
+  <si>
+    <t>카드 등급</t>
+  </si>
+  <si>
+    <t>카드 일련번호</t>
+  </si>
+  <si>
+    <t>나라기호</t>
+  </si>
+  <si>
+    <t>수취인명</t>
+  </si>
+  <si>
+    <t>연락처</t>
+  </si>
+  <si>
+    <t>주소</t>
+  </si>
+  <si>
+    <t>우편번호</t>
+  </si>
+  <si>
+    <t>로고 이미지 목록</t>
+  </si>
+  <si>
+    <t>로고 이미지 파일</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="10"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <sz val="9"/>
+      <b/>
+      <sz val="10"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <b val="1"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6EAF8"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F3F4"/>
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F5E3"/>
+        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCF3CF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8DAEF"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
@@ -86,116 +193,70 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color indexed="64"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="5">
+    <cellStyle name="60% - 강조색1" xfId="4" builtinId="32"/>
+    <cellStyle name="나쁨" xfId="2" builtinId="27"/>
+    <cellStyle name="보통" xfId="3" builtinId="28"/>
+    <cellStyle name="좋음" xfId="1" builtinId="26"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -483,245 +544,159 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
+    <col min="1" max="1" width="14.1875" customWidth="1"/>
+    <col min="2" max="2" width="10.25" customWidth="1"/>
+    <col min="3" max="3" width="12.8125" customWidth="1"/>
+    <col min="4" max="4" width="14.625" customWidth="1"/>
+    <col min="5" max="6" width="11.8125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.8125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.8125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.8125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.1875" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>주문확인</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>주문확인</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>티셔츠 작업용</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>티셔츠 작업용</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>티셔츠 작업용</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>티셔츠 작업용</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>티셔츠 작업용</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>티셔츠 작업용</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>티셔츠 작업용</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>카드 포장용</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>카드 포장용</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="inlineStr">
-        <is>
-          <t>카드 포장용</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>택배송장정보</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>택배송장정보</t>
-        </is>
-      </c>
-      <c r="O1" s="4" t="inlineStr">
-        <is>
-          <t>택배송장정보</t>
-        </is>
-      </c>
-      <c r="P1" s="4" t="inlineStr">
-        <is>
-          <t>택배송장정보</t>
-        </is>
-      </c>
-      <c r="Q1" s="4" t="inlineStr">
-        <is>
-          <t>택배송장정보</t>
-        </is>
-      </c>
-      <c r="R1" s="5" t="inlineStr">
-        <is>
-          <t>프로젝트 관리</t>
-        </is>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>작업지시번호</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>주문번호</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>티셔츠 사이즈</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>티셔츠 컬러</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>티셔츠 종류</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>티셔츠 일련번호</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>실리콘 마크QR값</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>디자인QR값</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>홀로그램QR값</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>카드 바코드값</t>
-        </is>
-      </c>
-      <c r="K2" s="6" t="inlineStr">
-        <is>
-          <t>카드 등급</t>
-        </is>
-      </c>
-      <c r="L2" s="6" t="inlineStr">
-        <is>
-          <t>카드 일련번호</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
-          <t>나라기호</t>
-        </is>
-      </c>
-      <c r="N2" s="6" t="inlineStr">
-        <is>
-          <t>수취인명</t>
-        </is>
-      </c>
-      <c r="O2" s="6" t="inlineStr">
-        <is>
-          <t>연락처</t>
-        </is>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>주소</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>우편번호</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>프로젝트 완료일</t>
-        </is>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.6">
+      <c r="A2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>로고 이미지 목록</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>로고 이미지 파일</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.6">
+      <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>